--- a/data/trans_bre/IMC_inf_MED_R3-Dificultad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R3-Dificultad-trans_bre.xlsx
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-11.86603309935196</v>
+        <v>-10.89502888038161</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-7.320582231739126</v>
+        <v>-8.554561604497826</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-16.57675528790644</v>
+        <v>-15.13396825579129</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.3194001067844686</v>
+        <v>-0.3123734235665281</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.3234211798501672</v>
+        <v>-0.3882910675342749</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.5045492611179224</v>
+        <v>-0.4751114612272251</v>
       </c>
     </row>
     <row r="5">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-19.83931901165599</v>
+        <v>-17.71062038089031</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-13.92973121689656</v>
+        <v>-14.70820677908863</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-33.44343559666631</v>
+        <v>-32.84756015286258</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.4787963615797298</v>
+        <v>-0.4646737621588987</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.525995907232751</v>
+        <v>-0.5696841808426081</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.7952617955234377</v>
+        <v>-0.7935772774775967</v>
       </c>
     </row>
     <row r="6">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-3.303456680198328</v>
+        <v>-3.200287348749791</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-0.8208878102096414</v>
+        <v>-2.650460480625619</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.869405939229507</v>
+        <v>0.9438989976806857</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.09316852359653113</v>
+        <v>-0.09338372018591683</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.02834399287255254</v>
+        <v>-0.1298707760343702</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.1672423680185002</v>
+        <v>0.07055202846371517</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-1.91586604820653</v>
+        <v>-1.057245573218865</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-9.095780466864582</v>
+        <v>-8.968269418910722</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-3.113361093067653</v>
+        <v>-2.108104665888205</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.07727410499808486</v>
+        <v>-0.04569174477473837</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.4222061179055133</v>
+        <v>-0.4342268848658648</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2035324457222425</v>
+        <v>-0.1439420819708818</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-9.29961467645793</v>
+        <v>-8.405777998722327</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-16.51753638844226</v>
+        <v>-15.76972716986507</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-12.06195030772526</v>
+        <v>-11.95073379241733</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.3354116397145219</v>
+        <v>-0.3209605251486317</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.6437352181862335</v>
+        <v>-0.6574157953133658</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.6414815550931235</v>
+        <v>-0.6047780339066413</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>6.677415239504154</v>
+        <v>5.825231761260487</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-1.6554424416954</v>
+        <v>-2.498428227388081</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>6.607250430453095</v>
+        <v>7.868277366482925</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3270746094621617</v>
+        <v>0.3009638448578619</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.08275944150569912</v>
+        <v>-0.1248501737470052</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.6653767351987012</v>
+        <v>0.8010564722793473</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-0.456320534017704</v>
+        <v>1.565687726889392</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-2.112811298544992</v>
+        <v>-2.287499929963585</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-12.61184797539905</v>
+        <v>-11.83950835458479</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.02539239157241227</v>
+        <v>0.1068450158601263</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.1170467224493039</v>
+        <v>-0.1364764538345521</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.5961492807403002</v>
+        <v>-0.5908074890147761</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-8.625115913534383</v>
+        <v>-5.86454443664386</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-11.17814739462528</v>
+        <v>-9.609064272094262</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-21.0776814570912</v>
+        <v>-20.5575511564039</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.3947829729912893</v>
+        <v>-0.3193871630131844</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.4865407139127175</v>
+        <v>-0.474745402147899</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.8046991772914031</v>
+        <v>-0.8081031170013576</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>8.594904449987215</v>
+        <v>8.431793021973329</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5.361672986891768</v>
+        <v>4.961894313768374</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-4.689826084446006</v>
+        <v>-3.818616192834758</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.6561111527637549</v>
+        <v>0.7157746702168303</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.3696108654428153</v>
+        <v>0.4024791113317867</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.2612759704889353</v>
+        <v>-0.2070223830230176</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-9.20031127953137</v>
+        <v>-5.921120135333307</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-12.6076089295776</v>
+        <v>-7.670584848304054</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-4.889228284726064</v>
+        <v>-3.740616181873694</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.3402446282812954</v>
+        <v>-0.2264117935919229</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.5708727528339114</v>
+        <v>-0.4163496935686434</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.3090387223700919</v>
+        <v>-0.2454042697810243</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-21.82379550842375</v>
+        <v>-17.59725877737998</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-23.35166108872021</v>
+        <v>-17.03192553405454</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-15.76475873497689</v>
+        <v>-13.67703507580312</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.6430643735661822</v>
+        <v>-0.5614820699412804</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.8193024050418644</v>
+        <v>-0.716217609567284</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.7131520411309877</v>
+        <v>-0.6635913774725184</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2.969747562930082</v>
+        <v>6.973197863207221</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>-1.372159028985003</v>
+        <v>1.603103205494809</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>4.895554607107787</v>
+        <v>5.490394799921319</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.1582917120220304</v>
+        <v>0.3738572777369825</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.02846064933589628</v>
+        <v>0.1794118675985262</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.581987303054006</v>
+        <v>0.5697764547118824</v>
       </c>
     </row>
     <row r="16">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-5.977743381593642</v>
+        <v>-4.557311231404371</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-7.33548525631664</v>
+        <v>-7.233663824326666</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-8.758482705506463</v>
+        <v>-7.742816248083257</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.2144379650640822</v>
+        <v>-0.1770402085263411</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.3443632895847583</v>
+        <v>-0.3596452914614154</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.4385395440731849</v>
+        <v>-0.4039331148793117</v>
       </c>
     </row>
     <row r="17">
@@ -958,22 +958,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-10.62041728683311</v>
+        <v>-8.708610325721407</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-11.0670363391374</v>
+        <v>-10.47604909894399</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-13.92868145000863</v>
+        <v>-13.01023359450311</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.3491593370675538</v>
+        <v>-0.319854792583975</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.4691996732582721</v>
+        <v>-0.4818826154923454</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.6225062465810931</v>
+        <v>-0.5971885858955575</v>
       </c>
     </row>
     <row r="18">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>-1.32726241059456</v>
+        <v>-0.7719922597299007</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-3.039234556422698</v>
+        <v>-3.768180928182765</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-3.116414786256274</v>
+        <v>-3.097204030225785</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-0.04938550672525213</v>
+        <v>-0.03273184960890782</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.1571081486394442</v>
+        <v>-0.2029907473986497</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.1729267538592883</v>
+        <v>-0.1888535266592621</v>
       </c>
     </row>
     <row r="19">
